--- a/code/outputs/问题一/问题一_MILP_求解结果_result1提交格式.xlsx
+++ b/code/outputs/问题一/问题一_MILP_求解结果_result1提交格式.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="Rf0756700125349cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="R69078cf0ee914e91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="计划购电量" sheetId="1" r:id="Rf24d77504e4945dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="充放电量" sheetId="2" r:id="R6a987c13f1f44c77"/>
   </x:sheets>
 </x:workbook>
 </file>
